--- a/data_cache/excel/INDOTHAI_historical.xlsx
+++ b/data_cache/excel/INDOTHAI_historical.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E154"/>
+  <dimension ref="A1:G194"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -429,15 +429,25 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>traded_quantity</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>delivery_quantity</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>delivery_pct</t>
         </is>
@@ -446,2907 +456,4825 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>328.45</v>
+        <v>261.75</v>
       </c>
       <c r="C2" t="n">
-        <v>247731</v>
+        <v>261.75</v>
       </c>
       <c r="D2" t="n">
-        <v>144958</v>
+        <v>261.75</v>
       </c>
       <c r="E2" t="n">
-        <v>58.51</v>
+        <v>70348</v>
+      </c>
+      <c r="F2" t="n">
+        <v>35318</v>
+      </c>
+      <c r="G2" t="n">
+        <v>50.2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2024-08-20</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>312.05</v>
+        <v>287.9</v>
       </c>
       <c r="C3" t="n">
-        <v>334816</v>
+        <v>287.9</v>
       </c>
       <c r="D3" t="n">
-        <v>231018</v>
+        <v>287.9</v>
       </c>
       <c r="E3" t="n">
-        <v>69</v>
+        <v>110261</v>
+      </c>
+      <c r="F3" t="n">
+        <v>54135</v>
+      </c>
+      <c r="G3" t="n">
+        <v>49.1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>296.45</v>
+        <v>302</v>
       </c>
       <c r="C4" t="n">
-        <v>295463</v>
+        <v>302</v>
       </c>
       <c r="D4" t="n">
-        <v>152411</v>
+        <v>302</v>
       </c>
       <c r="E4" t="n">
-        <v>51.58</v>
+        <v>135843</v>
+      </c>
+      <c r="F4" t="n">
+        <v>86467</v>
+      </c>
+      <c r="G4" t="n">
+        <v>63.65</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>281.65</v>
+        <v>332.2</v>
       </c>
       <c r="C5" t="n">
-        <v>240972</v>
+        <v>332.2</v>
       </c>
       <c r="D5" t="n">
-        <v>124350</v>
+        <v>332.2</v>
       </c>
       <c r="E5" t="n">
-        <v>51.6</v>
+        <v>158742</v>
+      </c>
+      <c r="F5" t="n">
+        <v>83560</v>
+      </c>
+      <c r="G5" t="n">
+        <v>52.64</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>267.6</v>
+        <v>348.8</v>
       </c>
       <c r="C6" t="n">
-        <v>875237</v>
+        <v>348.8</v>
       </c>
       <c r="D6" t="n">
-        <v>599823</v>
+        <v>348.8</v>
       </c>
       <c r="E6" t="n">
-        <v>68.53</v>
+        <v>81681</v>
+      </c>
+      <c r="F6" t="n">
+        <v>76889</v>
+      </c>
+      <c r="G6" t="n">
+        <v>94.13</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>254.25</v>
+        <v>366.2</v>
       </c>
       <c r="C7" t="n">
-        <v>4403667</v>
+        <v>366.2</v>
       </c>
       <c r="D7" t="n">
-        <v>2456829</v>
+        <v>366.2</v>
       </c>
       <c r="E7" t="n">
-        <v>55.79</v>
+        <v>8014</v>
+      </c>
+      <c r="F7" t="n">
+        <v>8014</v>
+      </c>
+      <c r="G7" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>253.45</v>
+        <v>378.5</v>
       </c>
       <c r="C8" t="n">
-        <v>4621172</v>
+        <v>378.5</v>
       </c>
       <c r="D8" t="n">
-        <v>1474472</v>
+        <v>378.5</v>
       </c>
       <c r="E8" t="n">
-        <v>31.91</v>
+        <v>362151</v>
+      </c>
+      <c r="F8" t="n">
+        <v>169931</v>
+      </c>
+      <c r="G8" t="n">
+        <v>46.92</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>252.8</v>
+        <v>397.4</v>
       </c>
       <c r="C9" t="n">
-        <v>471633</v>
+        <v>397.4</v>
       </c>
       <c r="D9" t="n">
-        <v>232584</v>
+        <v>397.4</v>
       </c>
       <c r="E9" t="n">
-        <v>49.31</v>
+        <v>140808</v>
+      </c>
+      <c r="F9" t="n">
+        <v>103965</v>
+      </c>
+      <c r="G9" t="n">
+        <v>73.83</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>244.3</v>
+        <v>417.25</v>
       </c>
       <c r="C10" t="n">
-        <v>1514971</v>
+        <v>417.25</v>
       </c>
       <c r="D10" t="n">
-        <v>520191</v>
+        <v>417.25</v>
       </c>
       <c r="E10" t="n">
-        <v>34.34</v>
+        <v>65147</v>
+      </c>
+      <c r="F10" t="n">
+        <v>41700</v>
+      </c>
+      <c r="G10" t="n">
+        <v>64.01000000000001</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>252.75</v>
+        <v>421.9</v>
       </c>
       <c r="C11" t="n">
-        <v>912369</v>
+        <v>421.9</v>
       </c>
       <c r="D11" t="n">
-        <v>526876</v>
+        <v>421.9</v>
       </c>
       <c r="E11" t="n">
-        <v>57.75</v>
+        <v>191113</v>
+      </c>
+      <c r="F11" t="n">
+        <v>86276</v>
+      </c>
+      <c r="G11" t="n">
+        <v>45.14</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>250</v>
+        <v>442.95</v>
       </c>
       <c r="C12" t="n">
-        <v>613991</v>
+        <v>442.95</v>
       </c>
       <c r="D12" t="n">
-        <v>329494</v>
+        <v>442.95</v>
       </c>
       <c r="E12" t="n">
-        <v>53.66</v>
+        <v>115862</v>
+      </c>
+      <c r="F12" t="n">
+        <v>67342</v>
+      </c>
+      <c r="G12" t="n">
+        <v>58.12</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>259.2</v>
+        <v>463.85</v>
       </c>
       <c r="C13" t="n">
-        <v>1188462</v>
+        <v>463.85</v>
       </c>
       <c r="D13" t="n">
-        <v>395428</v>
+        <v>463.85</v>
       </c>
       <c r="E13" t="n">
-        <v>33.27</v>
+        <v>161368</v>
+      </c>
+      <c r="F13" t="n">
+        <v>103083</v>
+      </c>
+      <c r="G13" t="n">
+        <v>63.88</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>263.75</v>
+        <v>487</v>
       </c>
       <c r="C14" t="n">
-        <v>303611</v>
+        <v>487</v>
       </c>
       <c r="D14" t="n">
-        <v>149341</v>
+        <v>487</v>
       </c>
       <c r="E14" t="n">
-        <v>49.19</v>
+        <v>112687</v>
+      </c>
+      <c r="F14" t="n">
+        <v>71568</v>
+      </c>
+      <c r="G14" t="n">
+        <v>63.51</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>263.75</v>
+        <v>511.35</v>
       </c>
       <c r="C15" t="n">
-        <v>303611</v>
+        <v>511.35</v>
       </c>
       <c r="D15" t="n">
-        <v>149341</v>
+        <v>511.35</v>
       </c>
       <c r="E15" t="n">
-        <v>49.19</v>
+        <v>205000</v>
+      </c>
+      <c r="F15" t="n">
+        <v>123343</v>
+      </c>
+      <c r="G15" t="n">
+        <v>60.17</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2024-12-09</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>261.85</v>
+        <v>1141.3</v>
       </c>
       <c r="C16" t="n">
-        <v>668935</v>
+        <v>1141.3</v>
       </c>
       <c r="D16" t="n">
-        <v>393601</v>
+        <v>1141.3</v>
       </c>
       <c r="E16" t="n">
-        <v>58.84</v>
+        <v>15989</v>
+      </c>
+      <c r="F16" t="n">
+        <v>11557</v>
+      </c>
+      <c r="G16" t="n">
+        <v>72.28</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2024-12-10</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>269.15</v>
+        <v>1139.1</v>
       </c>
       <c r="C17" t="n">
-        <v>512305</v>
+        <v>1139.1</v>
       </c>
       <c r="D17" t="n">
-        <v>286180</v>
+        <v>1139.1</v>
       </c>
       <c r="E17" t="n">
-        <v>55.86</v>
+        <v>10779</v>
+      </c>
+      <c r="F17" t="n">
+        <v>8218</v>
+      </c>
+      <c r="G17" t="n">
+        <v>76.23999999999999</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2024-12-11</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>275.15</v>
+        <v>1137.45</v>
       </c>
       <c r="C18" t="n">
-        <v>1041825</v>
+        <v>1137.45</v>
       </c>
       <c r="D18" t="n">
-        <v>552283</v>
+        <v>1137.45</v>
       </c>
       <c r="E18" t="n">
-        <v>53.01</v>
+        <v>6372</v>
+      </c>
+      <c r="F18" t="n">
+        <v>5550</v>
+      </c>
+      <c r="G18" t="n">
+        <v>87.09999999999999</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>267.8</v>
+        <v>194.97</v>
       </c>
       <c r="C19" t="n">
-        <v>625136</v>
+        <v>194.97</v>
       </c>
       <c r="D19" t="n">
-        <v>298941</v>
+        <v>194.97</v>
       </c>
       <c r="E19" t="n">
-        <v>47.82</v>
+        <v>231208</v>
+      </c>
+      <c r="F19" t="n">
+        <v>158556</v>
+      </c>
+      <c r="G19" t="n">
+        <v>68.58</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>259.05</v>
+        <v>189.48</v>
       </c>
       <c r="C20" t="n">
-        <v>478208</v>
+        <v>189.48</v>
       </c>
       <c r="D20" t="n">
-        <v>284742</v>
+        <v>189.48</v>
       </c>
       <c r="E20" t="n">
-        <v>59.54</v>
+        <v>696168</v>
+      </c>
+      <c r="F20" t="n">
+        <v>392891</v>
+      </c>
+      <c r="G20" t="n">
+        <v>56.44</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>248.3</v>
+        <v>198.95</v>
       </c>
       <c r="C21" t="n">
-        <v>337452</v>
+        <v>198.95</v>
       </c>
       <c r="D21" t="n">
-        <v>176278</v>
+        <v>198.95</v>
       </c>
       <c r="E21" t="n">
-        <v>52.24</v>
+        <v>864322</v>
+      </c>
+      <c r="F21" t="n">
+        <v>620788</v>
+      </c>
+      <c r="G21" t="n">
+        <v>71.81999999999999</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>247.4</v>
+        <v>205.36</v>
       </c>
       <c r="C22" t="n">
-        <v>297207</v>
+        <v>205.36</v>
       </c>
       <c r="D22" t="n">
-        <v>121203</v>
+        <v>205.36</v>
       </c>
       <c r="E22" t="n">
-        <v>40.78</v>
+        <v>1664978</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1023429</v>
+      </c>
+      <c r="G22" t="n">
+        <v>61.47</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>245.7</v>
+        <v>210.75</v>
       </c>
       <c r="C23" t="n">
-        <v>218995</v>
+        <v>210.75</v>
       </c>
       <c r="D23" t="n">
-        <v>120157</v>
+        <v>210.75</v>
       </c>
       <c r="E23" t="n">
-        <v>54.87</v>
+        <v>2399631</v>
+      </c>
+      <c r="F23" t="n">
+        <v>977342</v>
+      </c>
+      <c r="G23" t="n">
+        <v>40.73</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>244.65</v>
+        <v>220.6</v>
       </c>
       <c r="C24" t="n">
-        <v>608627</v>
+        <v>220.6</v>
       </c>
       <c r="D24" t="n">
-        <v>291818</v>
+        <v>220.6</v>
       </c>
       <c r="E24" t="n">
-        <v>47.95</v>
+        <v>1130123</v>
+      </c>
+      <c r="F24" t="n">
+        <v>545056</v>
+      </c>
+      <c r="G24" t="n">
+        <v>48.23</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>240.7</v>
+        <v>230.8</v>
       </c>
       <c r="C25" t="n">
-        <v>1330838</v>
+        <v>230.8</v>
       </c>
       <c r="D25" t="n">
-        <v>515504</v>
+        <v>230.8</v>
       </c>
       <c r="E25" t="n">
-        <v>38.74</v>
+        <v>2179824</v>
+      </c>
+      <c r="F25" t="n">
+        <v>679085</v>
+      </c>
+      <c r="G25" t="n">
+        <v>31.15</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>242.01</v>
+        <v>240.28</v>
       </c>
       <c r="C26" t="n">
-        <v>336479</v>
+        <v>240.28</v>
       </c>
       <c r="D26" t="n">
-        <v>241376</v>
+        <v>240.28</v>
       </c>
       <c r="E26" t="n">
-        <v>71.73999999999999</v>
+        <v>959168</v>
+      </c>
+      <c r="F26" t="n">
+        <v>506242</v>
+      </c>
+      <c r="G26" t="n">
+        <v>52.78</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>245.97</v>
+        <v>248.29</v>
       </c>
       <c r="C27" t="n">
-        <v>491453</v>
+        <v>248.29</v>
       </c>
       <c r="D27" t="n">
-        <v>274261</v>
+        <v>248.29</v>
       </c>
       <c r="E27" t="n">
-        <v>55.81</v>
+        <v>1656915</v>
+      </c>
+      <c r="F27" t="n">
+        <v>944308</v>
+      </c>
+      <c r="G27" t="n">
+        <v>56.99</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>256.6</v>
+        <v>258.52</v>
       </c>
       <c r="C28" t="n">
-        <v>810649</v>
+        <v>258.52</v>
       </c>
       <c r="D28" t="n">
-        <v>354933</v>
+        <v>258.52</v>
       </c>
       <c r="E28" t="n">
-        <v>43.78</v>
+        <v>788046</v>
+      </c>
+      <c r="F28" t="n">
+        <v>431198</v>
+      </c>
+      <c r="G28" t="n">
+        <v>54.72</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>257.25</v>
+        <v>269.17</v>
       </c>
       <c r="C29" t="n">
-        <v>1843226</v>
+        <v>269.17</v>
       </c>
       <c r="D29" t="n">
-        <v>881483</v>
+        <v>269.17</v>
       </c>
       <c r="E29" t="n">
-        <v>47.82</v>
+        <v>1110617</v>
+      </c>
+      <c r="F29" t="n">
+        <v>566758</v>
+      </c>
+      <c r="G29" t="n">
+        <v>51.03</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>254.82</v>
+        <v>280.63</v>
       </c>
       <c r="C30" t="n">
-        <v>183079</v>
+        <v>280.63</v>
       </c>
       <c r="D30" t="n">
-        <v>92599</v>
+        <v>280.63</v>
       </c>
       <c r="E30" t="n">
-        <v>50.58</v>
+        <v>1354527</v>
+      </c>
+      <c r="F30" t="n">
+        <v>726387</v>
+      </c>
+      <c r="G30" t="n">
+        <v>53.63</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>247.86</v>
+        <v>293.25</v>
       </c>
       <c r="C31" t="n">
-        <v>1741117</v>
+        <v>293.25</v>
       </c>
       <c r="D31" t="n">
-        <v>428572</v>
+        <v>293.25</v>
       </c>
       <c r="E31" t="n">
-        <v>24.61</v>
+        <v>1216817</v>
+      </c>
+      <c r="F31" t="n">
+        <v>773651</v>
+      </c>
+      <c r="G31" t="n">
+        <v>63.58</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>253.27</v>
+        <v>305.05</v>
       </c>
       <c r="C32" t="n">
-        <v>510532</v>
+        <v>305.05</v>
       </c>
       <c r="D32" t="n">
-        <v>320044</v>
+        <v>305.05</v>
       </c>
       <c r="E32" t="n">
-        <v>62.69</v>
+        <v>1322398</v>
+      </c>
+      <c r="F32" t="n">
+        <v>680291</v>
+      </c>
+      <c r="G32" t="n">
+        <v>51.44</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>265.27</v>
+        <v>313.75</v>
       </c>
       <c r="C33" t="n">
-        <v>1549078</v>
+        <v>313.75</v>
       </c>
       <c r="D33" t="n">
-        <v>615937</v>
+        <v>313.75</v>
       </c>
       <c r="E33" t="n">
-        <v>39.76</v>
+        <v>2948018</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1726373</v>
+      </c>
+      <c r="G33" t="n">
+        <v>58.56</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>268.28</v>
+        <v>326.25</v>
       </c>
       <c r="C34" t="n">
-        <v>752311</v>
+        <v>326.25</v>
       </c>
       <c r="D34" t="n">
-        <v>422840</v>
+        <v>326.25</v>
       </c>
       <c r="E34" t="n">
-        <v>56.21</v>
+        <v>2143627</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1036444</v>
+      </c>
+      <c r="G34" t="n">
+        <v>48.35</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>268.82</v>
+        <v>341.9</v>
       </c>
       <c r="C35" t="n">
-        <v>465791</v>
+        <v>341.9</v>
       </c>
       <c r="D35" t="n">
-        <v>246135</v>
+        <v>341.9</v>
       </c>
       <c r="E35" t="n">
-        <v>52.84</v>
+        <v>1276937</v>
+      </c>
+      <c r="F35" t="n">
+        <v>768400</v>
+      </c>
+      <c r="G35" t="n">
+        <v>60.18</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>262.61</v>
+        <v>358.95</v>
       </c>
       <c r="C36" t="n">
-        <v>431092</v>
+        <v>358.95</v>
       </c>
       <c r="D36" t="n">
-        <v>272195</v>
+        <v>358.95</v>
       </c>
       <c r="E36" t="n">
-        <v>63.14</v>
+        <v>2056820</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1103649</v>
+      </c>
+      <c r="G36" t="n">
+        <v>53.66</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>260.76</v>
+        <v>375.9</v>
       </c>
       <c r="C37" t="n">
-        <v>190937</v>
+        <v>375.9</v>
       </c>
       <c r="D37" t="n">
-        <v>114655</v>
+        <v>375.9</v>
       </c>
       <c r="E37" t="n">
-        <v>60.05</v>
+        <v>2298543</v>
+      </c>
+      <c r="F37" t="n">
+        <v>988410</v>
+      </c>
+      <c r="G37" t="n">
+        <v>43</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>255.07</v>
+        <v>328.45</v>
       </c>
       <c r="C38" t="n">
-        <v>381904</v>
+        <v>328.45</v>
       </c>
       <c r="D38" t="n">
-        <v>242997</v>
+        <v>328.45</v>
       </c>
       <c r="E38" t="n">
-        <v>63.63</v>
+        <v>247731</v>
+      </c>
+      <c r="F38" t="n">
+        <v>144958</v>
+      </c>
+      <c r="G38" t="n">
+        <v>58.51</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>259.6</v>
+        <v>312.05</v>
       </c>
       <c r="C39" t="n">
-        <v>631553</v>
+        <v>312.05</v>
       </c>
       <c r="D39" t="n">
-        <v>352283</v>
+        <v>312.05</v>
       </c>
       <c r="E39" t="n">
-        <v>55.78</v>
+        <v>334816</v>
+      </c>
+      <c r="F39" t="n">
+        <v>231018</v>
+      </c>
+      <c r="G39" t="n">
+        <v>69</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>254.59</v>
+        <v>296.45</v>
       </c>
       <c r="C40" t="n">
-        <v>517553</v>
+        <v>296.45</v>
       </c>
       <c r="D40" t="n">
-        <v>272937</v>
+        <v>296.45</v>
       </c>
       <c r="E40" t="n">
-        <v>52.74</v>
+        <v>295463</v>
+      </c>
+      <c r="F40" t="n">
+        <v>152411</v>
+      </c>
+      <c r="G40" t="n">
+        <v>51.58</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>251.15</v>
+        <v>281.65</v>
       </c>
       <c r="C41" t="n">
-        <v>266712</v>
+        <v>281.65</v>
       </c>
       <c r="D41" t="n">
-        <v>135481</v>
+        <v>281.65</v>
       </c>
       <c r="E41" t="n">
-        <v>50.8</v>
+        <v>240972</v>
+      </c>
+      <c r="F41" t="n">
+        <v>124350</v>
+      </c>
+      <c r="G41" t="n">
+        <v>51.6</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>252.15</v>
+        <v>267.6</v>
       </c>
       <c r="C42" t="n">
-        <v>217885</v>
+        <v>267.6</v>
       </c>
       <c r="D42" t="n">
-        <v>121791</v>
+        <v>267.6</v>
       </c>
       <c r="E42" t="n">
-        <v>55.9</v>
+        <v>875237</v>
+      </c>
+      <c r="F42" t="n">
+        <v>599823</v>
+      </c>
+      <c r="G42" t="n">
+        <v>68.53</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>262.66</v>
+        <v>254.25</v>
       </c>
       <c r="C43" t="n">
-        <v>882234</v>
+        <v>254.25</v>
       </c>
       <c r="D43" t="n">
-        <v>558913</v>
+        <v>254.25</v>
       </c>
       <c r="E43" t="n">
-        <v>63.35</v>
+        <v>4403667</v>
+      </c>
+      <c r="F43" t="n">
+        <v>2456829</v>
+      </c>
+      <c r="G43" t="n">
+        <v>55.79</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>272.97</v>
+        <v>253.45</v>
       </c>
       <c r="C44" t="n">
-        <v>1572055</v>
+        <v>253.45</v>
       </c>
       <c r="D44" t="n">
-        <v>732046</v>
+        <v>253.45</v>
       </c>
       <c r="E44" t="n">
-        <v>46.57</v>
+        <v>4621172</v>
+      </c>
+      <c r="F44" t="n">
+        <v>1474472</v>
+      </c>
+      <c r="G44" t="n">
+        <v>31.91</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>261.6</v>
+        <v>252.8</v>
       </c>
       <c r="C45" t="n">
-        <v>3032020</v>
+        <v>252.8</v>
       </c>
       <c r="D45" t="n">
-        <v>1644587</v>
+        <v>252.8</v>
       </c>
       <c r="E45" t="n">
-        <v>54.24</v>
+        <v>471633</v>
+      </c>
+      <c r="F45" t="n">
+        <v>232584</v>
+      </c>
+      <c r="G45" t="n">
+        <v>49.31</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>258.3</v>
+        <v>244.3</v>
       </c>
       <c r="C46" t="n">
-        <v>1395469</v>
+        <v>244.3</v>
       </c>
       <c r="D46" t="n">
-        <v>666837</v>
+        <v>244.3</v>
       </c>
       <c r="E46" t="n">
-        <v>47.79</v>
+        <v>1514971</v>
+      </c>
+      <c r="F46" t="n">
+        <v>520191</v>
+      </c>
+      <c r="G46" t="n">
+        <v>34.34</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>260.45</v>
+        <v>252.75</v>
       </c>
       <c r="C47" t="n">
-        <v>465403</v>
+        <v>252.75</v>
       </c>
       <c r="D47" t="n">
-        <v>269363</v>
+        <v>252.75</v>
       </c>
       <c r="E47" t="n">
-        <v>57.88</v>
+        <v>912369</v>
+      </c>
+      <c r="F47" t="n">
+        <v>526876</v>
+      </c>
+      <c r="G47" t="n">
+        <v>57.75</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>258.25</v>
+        <v>250</v>
       </c>
       <c r="C48" t="n">
-        <v>309846</v>
+        <v>250</v>
       </c>
       <c r="D48" t="n">
-        <v>210750</v>
+        <v>250</v>
       </c>
       <c r="E48" t="n">
-        <v>68.02</v>
+        <v>613991</v>
+      </c>
+      <c r="F48" t="n">
+        <v>329494</v>
+      </c>
+      <c r="G48" t="n">
+        <v>53.66</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>261.95</v>
+        <v>259.2</v>
       </c>
       <c r="C49" t="n">
-        <v>309912</v>
+        <v>259.2</v>
       </c>
       <c r="D49" t="n">
-        <v>207716</v>
+        <v>259.2</v>
       </c>
       <c r="E49" t="n">
-        <v>67.02</v>
+        <v>1188462</v>
+      </c>
+      <c r="F49" t="n">
+        <v>395428</v>
+      </c>
+      <c r="G49" t="n">
+        <v>33.27</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>260.3</v>
+        <v>263.75</v>
       </c>
       <c r="C50" t="n">
-        <v>242613</v>
+        <v>263.75</v>
       </c>
       <c r="D50" t="n">
-        <v>117593</v>
+        <v>263.75</v>
       </c>
       <c r="E50" t="n">
-        <v>48.47</v>
+        <v>303611</v>
+      </c>
+      <c r="F50" t="n">
+        <v>149341</v>
+      </c>
+      <c r="G50" t="n">
+        <v>49.19</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>261.05</v>
+        <v>263.75</v>
       </c>
       <c r="C51" t="n">
-        <v>483006</v>
+        <v>263.75</v>
       </c>
       <c r="D51" t="n">
-        <v>355358</v>
+        <v>263.75</v>
       </c>
       <c r="E51" t="n">
-        <v>73.56999999999999</v>
+        <v>303611</v>
+      </c>
+      <c r="F51" t="n">
+        <v>149341</v>
+      </c>
+      <c r="G51" t="n">
+        <v>49.19</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>261.6</v>
+        <v>261.85</v>
       </c>
       <c r="C52" t="n">
-        <v>511181</v>
+        <v>261.85</v>
       </c>
       <c r="D52" t="n">
-        <v>350770</v>
+        <v>261.85</v>
       </c>
       <c r="E52" t="n">
-        <v>68.62</v>
+        <v>668935</v>
+      </c>
+      <c r="F52" t="n">
+        <v>393601</v>
+      </c>
+      <c r="G52" t="n">
+        <v>58.84</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>248.75</v>
+        <v>269.15</v>
       </c>
       <c r="C53" t="n">
-        <v>814951</v>
+        <v>269.15</v>
       </c>
       <c r="D53" t="n">
-        <v>345605</v>
+        <v>269.15</v>
       </c>
       <c r="E53" t="n">
-        <v>42.41</v>
+        <v>512305</v>
+      </c>
+      <c r="F53" t="n">
+        <v>286180</v>
+      </c>
+      <c r="G53" t="n">
+        <v>55.86</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>250.2</v>
+        <v>275.15</v>
       </c>
       <c r="C54" t="n">
-        <v>934604</v>
+        <v>275.15</v>
       </c>
       <c r="D54" t="n">
-        <v>467019</v>
+        <v>275.15</v>
       </c>
       <c r="E54" t="n">
-        <v>49.97</v>
+        <v>1041825</v>
+      </c>
+      <c r="F54" t="n">
+        <v>552283</v>
+      </c>
+      <c r="G54" t="n">
+        <v>53.01</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>255.75</v>
+        <v>267.8</v>
       </c>
       <c r="C55" t="n">
-        <v>474896</v>
+        <v>267.8</v>
       </c>
       <c r="D55" t="n">
-        <v>268426</v>
+        <v>267.8</v>
       </c>
       <c r="E55" t="n">
-        <v>56.52</v>
+        <v>625136</v>
+      </c>
+      <c r="F55" t="n">
+        <v>298941</v>
+      </c>
+      <c r="G55" t="n">
+        <v>47.82</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>259.1</v>
+        <v>259.05</v>
       </c>
       <c r="C56" t="n">
-        <v>400295</v>
+        <v>259.05</v>
       </c>
       <c r="D56" t="n">
-        <v>211971</v>
+        <v>259.05</v>
       </c>
       <c r="E56" t="n">
-        <v>52.95</v>
+        <v>478208</v>
+      </c>
+      <c r="F56" t="n">
+        <v>284742</v>
+      </c>
+      <c r="G56" t="n">
+        <v>59.54</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>257.2</v>
+        <v>248.3</v>
       </c>
       <c r="C57" t="n">
-        <v>260691</v>
+        <v>248.3</v>
       </c>
       <c r="D57" t="n">
-        <v>130534</v>
+        <v>248.3</v>
       </c>
       <c r="E57" t="n">
-        <v>50.07</v>
+        <v>337452</v>
+      </c>
+      <c r="F57" t="n">
+        <v>176278</v>
+      </c>
+      <c r="G57" t="n">
+        <v>52.24</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>256.05</v>
+        <v>247.4</v>
       </c>
       <c r="C58" t="n">
-        <v>532831</v>
+        <v>247.4</v>
       </c>
       <c r="D58" t="n">
-        <v>245165</v>
+        <v>247.4</v>
       </c>
       <c r="E58" t="n">
-        <v>46.01</v>
+        <v>297207</v>
+      </c>
+      <c r="F58" t="n">
+        <v>121203</v>
+      </c>
+      <c r="G58" t="n">
+        <v>40.78</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>258.2</v>
+        <v>245.7</v>
       </c>
       <c r="C59" t="n">
-        <v>1027614</v>
+        <v>245.7</v>
       </c>
       <c r="D59" t="n">
-        <v>583049</v>
+        <v>245.7</v>
       </c>
       <c r="E59" t="n">
-        <v>56.74</v>
+        <v>218995</v>
+      </c>
+      <c r="F59" t="n">
+        <v>120157</v>
+      </c>
+      <c r="G59" t="n">
+        <v>54.87</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>270.85</v>
+        <v>244.65</v>
       </c>
       <c r="C60" t="n">
-        <v>784127</v>
+        <v>244.65</v>
       </c>
       <c r="D60" t="n">
-        <v>423175</v>
+        <v>244.65</v>
       </c>
       <c r="E60" t="n">
-        <v>53.97</v>
+        <v>608627</v>
+      </c>
+      <c r="F60" t="n">
+        <v>291818</v>
+      </c>
+      <c r="G60" t="n">
+        <v>47.95</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>281.9</v>
+        <v>240.7</v>
       </c>
       <c r="C61" t="n">
-        <v>1605812</v>
+        <v>240.7</v>
       </c>
       <c r="D61" t="n">
-        <v>1191845</v>
+        <v>240.7</v>
       </c>
       <c r="E61" t="n">
-        <v>74.22</v>
+        <v>1330838</v>
+      </c>
+      <c r="F61" t="n">
+        <v>515504</v>
+      </c>
+      <c r="G61" t="n">
+        <v>38.74</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>281.9</v>
+        <v>242.01</v>
       </c>
       <c r="C62" t="n">
-        <v>1605812</v>
+        <v>242.01</v>
       </c>
       <c r="D62" t="n">
-        <v>1191845</v>
+        <v>242.01</v>
       </c>
       <c r="E62" t="n">
-        <v>74.22</v>
+        <v>336479</v>
+      </c>
+      <c r="F62" t="n">
+        <v>241376</v>
+      </c>
+      <c r="G62" t="n">
+        <v>71.73999999999999</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>288.85</v>
+        <v>245.97</v>
       </c>
       <c r="C63" t="n">
-        <v>1378219</v>
+        <v>245.97</v>
       </c>
       <c r="D63" t="n">
-        <v>783475</v>
+        <v>245.97</v>
       </c>
       <c r="E63" t="n">
-        <v>56.85</v>
+        <v>491453</v>
+      </c>
+      <c r="F63" t="n">
+        <v>274261</v>
+      </c>
+      <c r="G63" t="n">
+        <v>55.81</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>287.2</v>
+        <v>256.6</v>
       </c>
       <c r="C64" t="n">
-        <v>506862</v>
+        <v>256.6</v>
       </c>
       <c r="D64" t="n">
-        <v>258183</v>
+        <v>256.6</v>
       </c>
       <c r="E64" t="n">
-        <v>50.94</v>
+        <v>810649</v>
+      </c>
+      <c r="F64" t="n">
+        <v>354933</v>
+      </c>
+      <c r="G64" t="n">
+        <v>43.78</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>295.4</v>
+        <v>257.25</v>
       </c>
       <c r="C65" t="n">
-        <v>512803</v>
+        <v>257.25</v>
       </c>
       <c r="D65" t="n">
-        <v>354106</v>
+        <v>257.25</v>
       </c>
       <c r="E65" t="n">
-        <v>69.05</v>
+        <v>1843226</v>
+      </c>
+      <c r="F65" t="n">
+        <v>881483</v>
+      </c>
+      <c r="G65" t="n">
+        <v>47.82</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>291.35</v>
+        <v>254.82</v>
       </c>
       <c r="C66" t="n">
-        <v>1347154</v>
+        <v>254.82</v>
       </c>
       <c r="D66" t="n">
-        <v>884671</v>
+        <v>254.82</v>
       </c>
       <c r="E66" t="n">
-        <v>65.67</v>
+        <v>183079</v>
+      </c>
+      <c r="F66" t="n">
+        <v>92599</v>
+      </c>
+      <c r="G66" t="n">
+        <v>50.58</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>295.95</v>
+        <v>247.86</v>
       </c>
       <c r="C67" t="n">
-        <v>1396468</v>
+        <v>247.86</v>
       </c>
       <c r="D67" t="n">
-        <v>972413</v>
+        <v>247.86</v>
       </c>
       <c r="E67" t="n">
-        <v>69.63</v>
+        <v>1741117</v>
+      </c>
+      <c r="F67" t="n">
+        <v>428572</v>
+      </c>
+      <c r="G67" t="n">
+        <v>24.61</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>290.95</v>
+        <v>253.27</v>
       </c>
       <c r="C68" t="n">
-        <v>1631012</v>
+        <v>253.27</v>
       </c>
       <c r="D68" t="n">
-        <v>1230668</v>
+        <v>253.27</v>
       </c>
       <c r="E68" t="n">
-        <v>75.45</v>
+        <v>510532</v>
+      </c>
+      <c r="F68" t="n">
+        <v>320044</v>
+      </c>
+      <c r="G68" t="n">
+        <v>62.69</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>290.2</v>
+        <v>265.27</v>
       </c>
       <c r="C69" t="n">
-        <v>1179486</v>
+        <v>265.27</v>
       </c>
       <c r="D69" t="n">
-        <v>770985</v>
+        <v>265.27</v>
       </c>
       <c r="E69" t="n">
-        <v>65.37</v>
+        <v>1549078</v>
+      </c>
+      <c r="F69" t="n">
+        <v>615937</v>
+      </c>
+      <c r="G69" t="n">
+        <v>39.76</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>290.1</v>
+        <v>268.28</v>
       </c>
       <c r="C70" t="n">
-        <v>858612</v>
+        <v>268.28</v>
       </c>
       <c r="D70" t="n">
-        <v>503766</v>
+        <v>268.28</v>
       </c>
       <c r="E70" t="n">
-        <v>58.67</v>
+        <v>752311</v>
+      </c>
+      <c r="F70" t="n">
+        <v>422840</v>
+      </c>
+      <c r="G70" t="n">
+        <v>56.21</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>290.8</v>
+        <v>268.82</v>
       </c>
       <c r="C71" t="n">
-        <v>180246</v>
+        <v>268.82</v>
       </c>
       <c r="D71" t="n">
-        <v>107214</v>
+        <v>268.82</v>
       </c>
       <c r="E71" t="n">
-        <v>59.48</v>
+        <v>465791</v>
+      </c>
+      <c r="F71" t="n">
+        <v>246135</v>
+      </c>
+      <c r="G71" t="n">
+        <v>52.84</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>282.75</v>
+        <v>262.61</v>
       </c>
       <c r="C72" t="n">
-        <v>628664</v>
+        <v>262.61</v>
       </c>
       <c r="D72" t="n">
-        <v>370220</v>
+        <v>262.61</v>
       </c>
       <c r="E72" t="n">
-        <v>58.89</v>
+        <v>431092</v>
+      </c>
+      <c r="F72" t="n">
+        <v>272195</v>
+      </c>
+      <c r="G72" t="n">
+        <v>63.14</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>284.65</v>
+        <v>260.76</v>
       </c>
       <c r="C73" t="n">
-        <v>944547</v>
+        <v>260.76</v>
       </c>
       <c r="D73" t="n">
-        <v>447303</v>
+        <v>260.76</v>
       </c>
       <c r="E73" t="n">
-        <v>47.36</v>
+        <v>190937</v>
+      </c>
+      <c r="F73" t="n">
+        <v>114655</v>
+      </c>
+      <c r="G73" t="n">
+        <v>60.05</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>290.6</v>
+        <v>255.07</v>
       </c>
       <c r="C74" t="n">
-        <v>558473</v>
+        <v>255.07</v>
       </c>
       <c r="D74" t="n">
-        <v>411695</v>
+        <v>255.07</v>
       </c>
       <c r="E74" t="n">
-        <v>73.72</v>
+        <v>381904</v>
+      </c>
+      <c r="F74" t="n">
+        <v>242997</v>
+      </c>
+      <c r="G74" t="n">
+        <v>63.63</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>308.5</v>
+        <v>259.6</v>
       </c>
       <c r="C75" t="n">
-        <v>657970</v>
+        <v>259.6</v>
       </c>
       <c r="D75" t="n">
-        <v>318624</v>
+        <v>259.6</v>
       </c>
       <c r="E75" t="n">
-        <v>48.43</v>
+        <v>631553</v>
+      </c>
+      <c r="F75" t="n">
+        <v>352283</v>
+      </c>
+      <c r="G75" t="n">
+        <v>55.78</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>308.75</v>
+        <v>254.59</v>
       </c>
       <c r="C76" t="n">
-        <v>1613435</v>
+        <v>254.59</v>
       </c>
       <c r="D76" t="n">
-        <v>907571</v>
+        <v>254.59</v>
       </c>
       <c r="E76" t="n">
-        <v>56.25</v>
+        <v>517553</v>
+      </c>
+      <c r="F76" t="n">
+        <v>272937</v>
+      </c>
+      <c r="G76" t="n">
+        <v>52.74</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>306.6</v>
+        <v>251.15</v>
       </c>
       <c r="C77" t="n">
-        <v>662072</v>
+        <v>251.15</v>
       </c>
       <c r="D77" t="n">
-        <v>336467</v>
+        <v>251.15</v>
       </c>
       <c r="E77" t="n">
-        <v>50.82</v>
+        <v>266712</v>
+      </c>
+      <c r="F77" t="n">
+        <v>135481</v>
+      </c>
+      <c r="G77" t="n">
+        <v>50.8</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>309.9</v>
+        <v>252.15</v>
       </c>
       <c r="C78" t="n">
-        <v>2245809</v>
+        <v>252.15</v>
       </c>
       <c r="D78" t="n">
-        <v>1611423</v>
+        <v>252.15</v>
       </c>
       <c r="E78" t="n">
-        <v>71.75</v>
+        <v>217885</v>
+      </c>
+      <c r="F78" t="n">
+        <v>121791</v>
+      </c>
+      <c r="G78" t="n">
+        <v>55.9</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>304.55</v>
+        <v>262.66</v>
       </c>
       <c r="C79" t="n">
-        <v>1195356</v>
+        <v>262.66</v>
       </c>
       <c r="D79" t="n">
-        <v>625851</v>
+        <v>262.66</v>
       </c>
       <c r="E79" t="n">
-        <v>52.36</v>
+        <v>882234</v>
+      </c>
+      <c r="F79" t="n">
+        <v>558913</v>
+      </c>
+      <c r="G79" t="n">
+        <v>63.35</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>296.85</v>
+        <v>272.97</v>
       </c>
       <c r="C80" t="n">
-        <v>580617</v>
+        <v>272.97</v>
       </c>
       <c r="D80" t="n">
-        <v>395628</v>
+        <v>272.97</v>
       </c>
       <c r="E80" t="n">
-        <v>68.14</v>
+        <v>1572055</v>
+      </c>
+      <c r="F80" t="n">
+        <v>732046</v>
+      </c>
+      <c r="G80" t="n">
+        <v>46.57</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>297.4</v>
+        <v>261.6</v>
       </c>
       <c r="C81" t="n">
-        <v>429160</v>
+        <v>261.6</v>
       </c>
       <c r="D81" t="n">
-        <v>261821</v>
+        <v>261.6</v>
       </c>
       <c r="E81" t="n">
-        <v>61.01</v>
+        <v>3032020</v>
+      </c>
+      <c r="F81" t="n">
+        <v>1644587</v>
+      </c>
+      <c r="G81" t="n">
+        <v>54.24</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>292.25</v>
+        <v>258.3</v>
       </c>
       <c r="C82" t="n">
-        <v>685490</v>
+        <v>258.3</v>
       </c>
       <c r="D82" t="n">
-        <v>350315</v>
+        <v>258.3</v>
       </c>
       <c r="E82" t="n">
-        <v>51.1</v>
+        <v>1395469</v>
+      </c>
+      <c r="F82" t="n">
+        <v>666837</v>
+      </c>
+      <c r="G82" t="n">
+        <v>47.79</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>296.95</v>
+        <v>260.45</v>
       </c>
       <c r="C83" t="n">
-        <v>1181301</v>
+        <v>260.45</v>
       </c>
       <c r="D83" t="n">
-        <v>564989</v>
+        <v>260.45</v>
       </c>
       <c r="E83" t="n">
-        <v>47.83</v>
+        <v>465403</v>
+      </c>
+      <c r="F83" t="n">
+        <v>269363</v>
+      </c>
+      <c r="G83" t="n">
+        <v>57.88</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>287.85</v>
+        <v>258.25</v>
       </c>
       <c r="C84" t="n">
-        <v>468467</v>
+        <v>258.25</v>
       </c>
       <c r="D84" t="n">
-        <v>267637</v>
+        <v>258.25</v>
       </c>
       <c r="E84" t="n">
-        <v>57.13</v>
+        <v>309846</v>
+      </c>
+      <c r="F84" t="n">
+        <v>210750</v>
+      </c>
+      <c r="G84" t="n">
+        <v>68.02</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>290.25</v>
+        <v>261.95</v>
       </c>
       <c r="C85" t="n">
-        <v>880515</v>
+        <v>261.95</v>
       </c>
       <c r="D85" t="n">
-        <v>406878</v>
+        <v>261.95</v>
       </c>
       <c r="E85" t="n">
-        <v>46.21</v>
+        <v>309912</v>
+      </c>
+      <c r="F85" t="n">
+        <v>207716</v>
+      </c>
+      <c r="G85" t="n">
+        <v>67.02</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>292.95</v>
+        <v>260.3</v>
       </c>
       <c r="C86" t="n">
-        <v>1038602</v>
+        <v>260.3</v>
       </c>
       <c r="D86" t="n">
-        <v>668330</v>
+        <v>260.3</v>
       </c>
       <c r="E86" t="n">
-        <v>64.34999999999999</v>
+        <v>242613</v>
+      </c>
+      <c r="F86" t="n">
+        <v>117593</v>
+      </c>
+      <c r="G86" t="n">
+        <v>48.47</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>290.4</v>
+        <v>261.05</v>
       </c>
       <c r="C87" t="n">
-        <v>525888</v>
+        <v>261.05</v>
       </c>
       <c r="D87" t="n">
-        <v>286475</v>
+        <v>261.05</v>
       </c>
       <c r="E87" t="n">
-        <v>54.47</v>
+        <v>483006</v>
+      </c>
+      <c r="F87" t="n">
+        <v>355358</v>
+      </c>
+      <c r="G87" t="n">
+        <v>73.56999999999999</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>305.75</v>
+        <v>261.6</v>
       </c>
       <c r="C88" t="n">
-        <v>1305781</v>
+        <v>261.6</v>
       </c>
       <c r="D88" t="n">
-        <v>356444</v>
+        <v>261.6</v>
       </c>
       <c r="E88" t="n">
-        <v>27.3</v>
+        <v>511181</v>
+      </c>
+      <c r="F88" t="n">
+        <v>350770</v>
+      </c>
+      <c r="G88" t="n">
+        <v>68.62</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>297.05</v>
+        <v>248.75</v>
       </c>
       <c r="C89" t="n">
-        <v>1777778</v>
+        <v>248.75</v>
       </c>
       <c r="D89" t="n">
-        <v>631739</v>
+        <v>248.75</v>
       </c>
       <c r="E89" t="n">
-        <v>35.54</v>
+        <v>814951</v>
+      </c>
+      <c r="F89" t="n">
+        <v>345605</v>
+      </c>
+      <c r="G89" t="n">
+        <v>42.41</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>288.85</v>
+        <v>250.2</v>
       </c>
       <c r="C90" t="n">
-        <v>390445</v>
+        <v>250.2</v>
       </c>
       <c r="D90" t="n">
-        <v>213229</v>
+        <v>250.2</v>
       </c>
       <c r="E90" t="n">
-        <v>54.61</v>
+        <v>934604</v>
+      </c>
+      <c r="F90" t="n">
+        <v>467019</v>
+      </c>
+      <c r="G90" t="n">
+        <v>49.97</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>280.85</v>
+        <v>255.75</v>
       </c>
       <c r="C91" t="n">
-        <v>335430</v>
+        <v>255.75</v>
       </c>
       <c r="D91" t="n">
-        <v>172284</v>
+        <v>255.75</v>
       </c>
       <c r="E91" t="n">
-        <v>51.36</v>
+        <v>474896</v>
+      </c>
+      <c r="F91" t="n">
+        <v>268426</v>
+      </c>
+      <c r="G91" t="n">
+        <v>56.52</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>274.55</v>
+        <v>259.1</v>
       </c>
       <c r="C92" t="n">
-        <v>270348</v>
+        <v>259.1</v>
       </c>
       <c r="D92" t="n">
-        <v>110082</v>
+        <v>259.1</v>
       </c>
       <c r="E92" t="n">
-        <v>40.72</v>
+        <v>400295</v>
+      </c>
+      <c r="F92" t="n">
+        <v>211971</v>
+      </c>
+      <c r="G92" t="n">
+        <v>52.95</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>273.1</v>
+        <v>257.2</v>
       </c>
       <c r="C93" t="n">
-        <v>349641</v>
+        <v>257.2</v>
       </c>
       <c r="D93" t="n">
-        <v>139364</v>
+        <v>257.2</v>
       </c>
       <c r="E93" t="n">
-        <v>39.86</v>
+        <v>260691</v>
+      </c>
+      <c r="F93" t="n">
+        <v>130534</v>
+      </c>
+      <c r="G93" t="n">
+        <v>50.07</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>269.3</v>
+        <v>256.05</v>
       </c>
       <c r="C94" t="n">
-        <v>539106</v>
+        <v>256.05</v>
       </c>
       <c r="D94" t="n">
-        <v>199572</v>
+        <v>256.05</v>
       </c>
       <c r="E94" t="n">
-        <v>37.02</v>
+        <v>532831</v>
+      </c>
+      <c r="F94" t="n">
+        <v>245165</v>
+      </c>
+      <c r="G94" t="n">
+        <v>46.01</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>269.05</v>
+        <v>258.2</v>
       </c>
       <c r="C95" t="n">
-        <v>283519</v>
+        <v>258.2</v>
       </c>
       <c r="D95" t="n">
-        <v>123979</v>
+        <v>258.2</v>
       </c>
       <c r="E95" t="n">
-        <v>43.73</v>
+        <v>1027614</v>
+      </c>
+      <c r="F95" t="n">
+        <v>583049</v>
+      </c>
+      <c r="G95" t="n">
+        <v>56.74</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>268.5</v>
+        <v>270.85</v>
       </c>
       <c r="C96" t="n">
-        <v>555421</v>
+        <v>270.85</v>
       </c>
       <c r="D96" t="n">
-        <v>296794</v>
+        <v>270.85</v>
       </c>
       <c r="E96" t="n">
-        <v>53.44</v>
+        <v>784127</v>
+      </c>
+      <c r="F96" t="n">
+        <v>423175</v>
+      </c>
+      <c r="G96" t="n">
+        <v>53.97</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>272.2</v>
+        <v>281.9</v>
       </c>
       <c r="C97" t="n">
-        <v>350722</v>
+        <v>281.9</v>
       </c>
       <c r="D97" t="n">
-        <v>210522</v>
+        <v>281.9</v>
       </c>
       <c r="E97" t="n">
-        <v>60.03</v>
+        <v>1605812</v>
+      </c>
+      <c r="F97" t="n">
+        <v>1191845</v>
+      </c>
+      <c r="G97" t="n">
+        <v>74.22</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>270.05</v>
+        <v>281.9</v>
       </c>
       <c r="C98" t="n">
-        <v>1337576</v>
+        <v>281.9</v>
       </c>
       <c r="D98" t="n">
-        <v>1029809</v>
+        <v>281.9</v>
       </c>
       <c r="E98" t="n">
-        <v>76.98999999999999</v>
+        <v>1605812</v>
+      </c>
+      <c r="F98" t="n">
+        <v>1191845</v>
+      </c>
+      <c r="G98" t="n">
+        <v>74.22</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>252.65</v>
+        <v>288.85</v>
       </c>
       <c r="C99" t="n">
-        <v>1984131</v>
+        <v>288.85</v>
       </c>
       <c r="D99" t="n">
-        <v>1271887</v>
+        <v>288.85</v>
       </c>
       <c r="E99" t="n">
-        <v>64.09999999999999</v>
+        <v>1378219</v>
+      </c>
+      <c r="F99" t="n">
+        <v>783475</v>
+      </c>
+      <c r="G99" t="n">
+        <v>56.85</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>238.9</v>
+        <v>287.2</v>
       </c>
       <c r="C100" t="n">
-        <v>1824784</v>
+        <v>287.2</v>
       </c>
       <c r="D100" t="n">
-        <v>669410</v>
+        <v>287.2</v>
       </c>
       <c r="E100" t="n">
-        <v>36.68</v>
+        <v>506862</v>
+      </c>
+      <c r="F100" t="n">
+        <v>258183</v>
+      </c>
+      <c r="G100" t="n">
+        <v>50.94</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>245.15</v>
+        <v>295.4</v>
       </c>
       <c r="C101" t="n">
-        <v>918268</v>
+        <v>295.4</v>
       </c>
       <c r="D101" t="n">
-        <v>314634</v>
+        <v>295.4</v>
       </c>
       <c r="E101" t="n">
-        <v>34.26</v>
+        <v>512803</v>
+      </c>
+      <c r="F101" t="n">
+        <v>354106</v>
+      </c>
+      <c r="G101" t="n">
+        <v>69.05</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>246.55</v>
+        <v>291.35</v>
       </c>
       <c r="C102" t="n">
-        <v>668194</v>
+        <v>291.35</v>
       </c>
       <c r="D102" t="n">
-        <v>258680</v>
+        <v>291.35</v>
       </c>
       <c r="E102" t="n">
-        <v>38.71</v>
+        <v>1347154</v>
+      </c>
+      <c r="F102" t="n">
+        <v>884671</v>
+      </c>
+      <c r="G102" t="n">
+        <v>65.67</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>246.55</v>
+        <v>295.95</v>
       </c>
       <c r="C103" t="n">
-        <v>668194</v>
+        <v>295.95</v>
       </c>
       <c r="D103" t="n">
-        <v>258680</v>
+        <v>295.95</v>
       </c>
       <c r="E103" t="n">
-        <v>38.71</v>
+        <v>1396468</v>
+      </c>
+      <c r="F103" t="n">
+        <v>972413</v>
+      </c>
+      <c r="G103" t="n">
+        <v>69.63</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>227.1</v>
+        <v>290.95</v>
       </c>
       <c r="C104" t="n">
-        <v>1105874</v>
+        <v>290.95</v>
       </c>
       <c r="D104" t="n">
-        <v>467344</v>
+        <v>290.95</v>
       </c>
       <c r="E104" t="n">
-        <v>42.26</v>
+        <v>1631012</v>
+      </c>
+      <c r="F104" t="n">
+        <v>1230668</v>
+      </c>
+      <c r="G104" t="n">
+        <v>75.45</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>226.57</v>
+        <v>290.2</v>
       </c>
       <c r="C105" t="n">
-        <v>1371586</v>
+        <v>290.2</v>
       </c>
       <c r="D105" t="n">
-        <v>750814</v>
+        <v>290.2</v>
       </c>
       <c r="E105" t="n">
-        <v>54.74</v>
+        <v>1179486</v>
+      </c>
+      <c r="F105" t="n">
+        <v>770985</v>
+      </c>
+      <c r="G105" t="n">
+        <v>65.37</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>228.66</v>
+        <v>290.1</v>
       </c>
       <c r="C106" t="n">
-        <v>468319</v>
+        <v>290.1</v>
       </c>
       <c r="D106" t="n">
-        <v>267139</v>
+        <v>290.1</v>
       </c>
       <c r="E106" t="n">
-        <v>57.04</v>
+        <v>858612</v>
+      </c>
+      <c r="F106" t="n">
+        <v>503766</v>
+      </c>
+      <c r="G106" t="n">
+        <v>58.67</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>226.87</v>
+        <v>290.8</v>
       </c>
       <c r="C107" t="n">
-        <v>516708</v>
+        <v>290.8</v>
       </c>
       <c r="D107" t="n">
-        <v>293088</v>
+        <v>290.8</v>
       </c>
       <c r="E107" t="n">
-        <v>56.72</v>
+        <v>180246</v>
+      </c>
+      <c r="F107" t="n">
+        <v>107214</v>
+      </c>
+      <c r="G107" t="n">
+        <v>59.48</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>216.24</v>
+        <v>282.75</v>
       </c>
       <c r="C108" t="n">
-        <v>756389</v>
+        <v>282.75</v>
       </c>
       <c r="D108" t="n">
-        <v>433202</v>
+        <v>282.75</v>
       </c>
       <c r="E108" t="n">
-        <v>57.27</v>
+        <v>628664</v>
+      </c>
+      <c r="F108" t="n">
+        <v>370220</v>
+      </c>
+      <c r="G108" t="n">
+        <v>58.89</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>233.76</v>
+        <v>284.65</v>
       </c>
       <c r="C109" t="n">
-        <v>1694529</v>
+        <v>284.65</v>
       </c>
       <c r="D109" t="n">
-        <v>430919</v>
+        <v>284.65</v>
       </c>
       <c r="E109" t="n">
-        <v>25.43</v>
+        <v>944547</v>
+      </c>
+      <c r="F109" t="n">
+        <v>447303</v>
+      </c>
+      <c r="G109" t="n">
+        <v>47.36</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>227.14</v>
+        <v>290.6</v>
       </c>
       <c r="C110" t="n">
-        <v>1333469</v>
+        <v>290.6</v>
       </c>
       <c r="D110" t="n">
-        <v>656423</v>
+        <v>290.6</v>
       </c>
       <c r="E110" t="n">
-        <v>49.23</v>
+        <v>558473</v>
+      </c>
+      <c r="F110" t="n">
+        <v>411695</v>
+      </c>
+      <c r="G110" t="n">
+        <v>73.72</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>229.7</v>
+        <v>308.5</v>
       </c>
       <c r="C111" t="n">
-        <v>558064</v>
+        <v>308.5</v>
       </c>
       <c r="D111" t="n">
-        <v>215891</v>
+        <v>308.5</v>
       </c>
       <c r="E111" t="n">
-        <v>38.69</v>
+        <v>657970</v>
+      </c>
+      <c r="F111" t="n">
+        <v>318624</v>
+      </c>
+      <c r="G111" t="n">
+        <v>48.43</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>235.7</v>
+        <v>308.75</v>
       </c>
       <c r="C112" t="n">
-        <v>1242149</v>
+        <v>308.75</v>
       </c>
       <c r="D112" t="n">
-        <v>590171</v>
+        <v>308.75</v>
       </c>
       <c r="E112" t="n">
-        <v>47.51</v>
+        <v>1613435</v>
+      </c>
+      <c r="F112" t="n">
+        <v>907571</v>
+      </c>
+      <c r="G112" t="n">
+        <v>56.25</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>239.18</v>
+        <v>306.6</v>
       </c>
       <c r="C113" t="n">
-        <v>1285925</v>
+        <v>306.6</v>
       </c>
       <c r="D113" t="n">
-        <v>429171</v>
+        <v>306.6</v>
       </c>
       <c r="E113" t="n">
-        <v>33.37</v>
+        <v>662072</v>
+      </c>
+      <c r="F113" t="n">
+        <v>336467</v>
+      </c>
+      <c r="G113" t="n">
+        <v>50.82</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>241.9</v>
+        <v>309.9</v>
       </c>
       <c r="C114" t="n">
-        <v>1609258</v>
+        <v>309.9</v>
       </c>
       <c r="D114" t="n">
-        <v>780486</v>
+        <v>309.9</v>
       </c>
       <c r="E114" t="n">
-        <v>48.5</v>
+        <v>2245809</v>
+      </c>
+      <c r="F114" t="n">
+        <v>1611423</v>
+      </c>
+      <c r="G114" t="n">
+        <v>71.75</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>236.7</v>
+        <v>304.55</v>
       </c>
       <c r="C115" t="n">
-        <v>892642</v>
+        <v>304.55</v>
       </c>
       <c r="D115" t="n">
-        <v>351371</v>
+        <v>304.55</v>
       </c>
       <c r="E115" t="n">
-        <v>39.36</v>
+        <v>1195356</v>
+      </c>
+      <c r="F115" t="n">
+        <v>625851</v>
+      </c>
+      <c r="G115" t="n">
+        <v>52.36</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>240.03</v>
+        <v>296.85</v>
       </c>
       <c r="C116" t="n">
-        <v>1275917</v>
+        <v>296.85</v>
       </c>
       <c r="D116" t="n">
-        <v>380688</v>
+        <v>296.85</v>
       </c>
       <c r="E116" t="n">
-        <v>29.84</v>
+        <v>580617</v>
+      </c>
+      <c r="F116" t="n">
+        <v>395628</v>
+      </c>
+      <c r="G116" t="n">
+        <v>68.14</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>238.09</v>
+        <v>297.4</v>
       </c>
       <c r="C117" t="n">
-        <v>1284474</v>
+        <v>297.4</v>
       </c>
       <c r="D117" t="n">
-        <v>604404</v>
+        <v>297.4</v>
       </c>
       <c r="E117" t="n">
-        <v>47.05</v>
+        <v>429160</v>
+      </c>
+      <c r="F117" t="n">
+        <v>261821</v>
+      </c>
+      <c r="G117" t="n">
+        <v>61.01</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>236.51</v>
+        <v>292.25</v>
       </c>
       <c r="C118" t="n">
-        <v>748214</v>
+        <v>292.25</v>
       </c>
       <c r="D118" t="n">
-        <v>243644</v>
+        <v>292.25</v>
       </c>
       <c r="E118" t="n">
-        <v>32.56</v>
+        <v>685490</v>
+      </c>
+      <c r="F118" t="n">
+        <v>350315</v>
+      </c>
+      <c r="G118" t="n">
+        <v>51.1</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>225.68</v>
+        <v>296.95</v>
       </c>
       <c r="C119" t="n">
-        <v>3789584</v>
+        <v>296.95</v>
       </c>
       <c r="D119" t="n">
-        <v>1194075</v>
+        <v>296.95</v>
       </c>
       <c r="E119" t="n">
-        <v>31.51</v>
+        <v>1181301</v>
+      </c>
+      <c r="F119" t="n">
+        <v>564989</v>
+      </c>
+      <c r="G119" t="n">
+        <v>47.83</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>225.02</v>
+        <v>287.85</v>
       </c>
       <c r="C120" t="n">
-        <v>1980280</v>
+        <v>287.85</v>
       </c>
       <c r="D120" t="n">
-        <v>696136</v>
+        <v>287.85</v>
       </c>
       <c r="E120" t="n">
-        <v>35.15</v>
+        <v>468467</v>
+      </c>
+      <c r="F120" t="n">
+        <v>267637</v>
+      </c>
+      <c r="G120" t="n">
+        <v>57.13</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>231.57</v>
+        <v>290.25</v>
       </c>
       <c r="C121" t="n">
-        <v>1348473</v>
+        <v>290.25</v>
       </c>
       <c r="D121" t="n">
-        <v>836695</v>
+        <v>290.25</v>
       </c>
       <c r="E121" t="n">
-        <v>62.05</v>
+        <v>880515</v>
+      </c>
+      <c r="F121" t="n">
+        <v>406878</v>
+      </c>
+      <c r="G121" t="n">
+        <v>46.21</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>231.58</v>
+        <v>292.95</v>
       </c>
       <c r="C122" t="n">
-        <v>820685</v>
+        <v>292.95</v>
       </c>
       <c r="D122" t="n">
-        <v>394520</v>
+        <v>292.95</v>
       </c>
       <c r="E122" t="n">
-        <v>48.07</v>
+        <v>1038602</v>
+      </c>
+      <c r="F122" t="n">
+        <v>668330</v>
+      </c>
+      <c r="G122" t="n">
+        <v>64.34999999999999</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>231.58</v>
+        <v>290.4</v>
       </c>
       <c r="C123" t="n">
-        <v>820685</v>
+        <v>290.4</v>
       </c>
       <c r="D123" t="n">
-        <v>394520</v>
+        <v>290.4</v>
       </c>
       <c r="E123" t="n">
-        <v>48.07</v>
+        <v>525888</v>
+      </c>
+      <c r="F123" t="n">
+        <v>286475</v>
+      </c>
+      <c r="G123" t="n">
+        <v>54.47</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>223.12</v>
+        <v>305.75</v>
       </c>
       <c r="C124" t="n">
-        <v>564135</v>
+        <v>305.75</v>
       </c>
       <c r="D124" t="n">
-        <v>254562</v>
+        <v>305.75</v>
       </c>
       <c r="E124" t="n">
-        <v>45.12</v>
+        <v>1305781</v>
+      </c>
+      <c r="F124" t="n">
+        <v>356444</v>
+      </c>
+      <c r="G124" t="n">
+        <v>27.3</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>227.06</v>
+        <v>297.05</v>
       </c>
       <c r="C125" t="n">
-        <v>592516</v>
+        <v>297.05</v>
       </c>
       <c r="D125" t="n">
-        <v>258309</v>
+        <v>297.05</v>
       </c>
       <c r="E125" t="n">
-        <v>43.6</v>
+        <v>1777778</v>
+      </c>
+      <c r="F125" t="n">
+        <v>631739</v>
+      </c>
+      <c r="G125" t="n">
+        <v>35.54</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>234.31</v>
+        <v>288.85</v>
       </c>
       <c r="C126" t="n">
-        <v>1140218</v>
+        <v>288.85</v>
       </c>
       <c r="D126" t="n">
-        <v>421273</v>
+        <v>288.85</v>
       </c>
       <c r="E126" t="n">
-        <v>36.95</v>
+        <v>390445</v>
+      </c>
+      <c r="F126" t="n">
+        <v>213229</v>
+      </c>
+      <c r="G126" t="n">
+        <v>54.61</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>248.43</v>
+        <v>280.85</v>
       </c>
       <c r="C127" t="n">
-        <v>2447922</v>
+        <v>280.85</v>
       </c>
       <c r="D127" t="n">
-        <v>627209</v>
+        <v>280.85</v>
       </c>
       <c r="E127" t="n">
-        <v>25.62</v>
+        <v>335430</v>
+      </c>
+      <c r="F127" t="n">
+        <v>172284</v>
+      </c>
+      <c r="G127" t="n">
+        <v>51.36</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>253.38</v>
+        <v>274.55</v>
       </c>
       <c r="C128" t="n">
-        <v>1778621</v>
+        <v>274.55</v>
       </c>
       <c r="D128" t="n">
-        <v>489187</v>
+        <v>274.55</v>
       </c>
       <c r="E128" t="n">
-        <v>27.5</v>
+        <v>270348</v>
+      </c>
+      <c r="F128" t="n">
+        <v>110082</v>
+      </c>
+      <c r="G128" t="n">
+        <v>40.72</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>240.72</v>
+        <v>273.1</v>
       </c>
       <c r="C129" t="n">
-        <v>1803394</v>
+        <v>273.1</v>
       </c>
       <c r="D129" t="n">
-        <v>342209</v>
+        <v>273.1</v>
       </c>
       <c r="E129" t="n">
-        <v>18.98</v>
+        <v>349641</v>
+      </c>
+      <c r="F129" t="n">
+        <v>139364</v>
+      </c>
+      <c r="G129" t="n">
+        <v>39.86</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>224.89</v>
+        <v>269.3</v>
       </c>
       <c r="C130" t="n">
-        <v>820448</v>
+        <v>269.3</v>
       </c>
       <c r="D130" t="n">
-        <v>347187</v>
+        <v>269.3</v>
       </c>
       <c r="E130" t="n">
-        <v>42.32</v>
+        <v>539106</v>
+      </c>
+      <c r="F130" t="n">
+        <v>199572</v>
+      </c>
+      <c r="G130" t="n">
+        <v>37.02</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>216.1</v>
+        <v>269.05</v>
       </c>
       <c r="C131" t="n">
-        <v>982645</v>
+        <v>269.05</v>
       </c>
       <c r="D131" t="n">
-        <v>396992</v>
+        <v>269.05</v>
       </c>
       <c r="E131" t="n">
-        <v>40.4</v>
+        <v>283519</v>
+      </c>
+      <c r="F131" t="n">
+        <v>123979</v>
+      </c>
+      <c r="G131" t="n">
+        <v>43.73</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>216.6</v>
+        <v>268.5</v>
       </c>
       <c r="C132" t="n">
-        <v>491358</v>
+        <v>268.5</v>
       </c>
       <c r="D132" t="n">
-        <v>289592</v>
+        <v>268.5</v>
       </c>
       <c r="E132" t="n">
-        <v>58.94</v>
+        <v>555421</v>
+      </c>
+      <c r="F132" t="n">
+        <v>296794</v>
+      </c>
+      <c r="G132" t="n">
+        <v>53.44</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>218.41</v>
+        <v>272.2</v>
       </c>
       <c r="C133" t="n">
-        <v>776940</v>
+        <v>272.2</v>
       </c>
       <c r="D133" t="n">
-        <v>462061</v>
+        <v>272.2</v>
       </c>
       <c r="E133" t="n">
-        <v>59.47</v>
+        <v>350722</v>
+      </c>
+      <c r="F133" t="n">
+        <v>210522</v>
+      </c>
+      <c r="G133" t="n">
+        <v>60.03</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>216.93</v>
+        <v>270.05</v>
       </c>
       <c r="C134" t="n">
-        <v>589194</v>
+        <v>270.05</v>
       </c>
       <c r="D134" t="n">
-        <v>252248</v>
+        <v>270.05</v>
       </c>
       <c r="E134" t="n">
-        <v>42.81</v>
+        <v>1337576</v>
+      </c>
+      <c r="F134" t="n">
+        <v>1029809</v>
+      </c>
+      <c r="G134" t="n">
+        <v>76.98999999999999</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>216.15</v>
+        <v>252.65</v>
       </c>
       <c r="C135" t="n">
-        <v>737195</v>
+        <v>252.65</v>
       </c>
       <c r="D135" t="n">
-        <v>401496</v>
+        <v>252.65</v>
       </c>
       <c r="E135" t="n">
-        <v>54.46</v>
+        <v>1984131</v>
+      </c>
+      <c r="F135" t="n">
+        <v>1271887</v>
+      </c>
+      <c r="G135" t="n">
+        <v>64.09999999999999</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>215.48</v>
+        <v>238.9</v>
       </c>
       <c r="C136" t="n">
-        <v>2051164</v>
+        <v>238.9</v>
       </c>
       <c r="D136" t="n">
-        <v>709077</v>
+        <v>238.9</v>
       </c>
       <c r="E136" t="n">
-        <v>34.57</v>
+        <v>1824784</v>
+      </c>
+      <c r="F136" t="n">
+        <v>669410</v>
+      </c>
+      <c r="G136" t="n">
+        <v>36.68</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>219.17</v>
+        <v>245.15</v>
       </c>
       <c r="C137" t="n">
-        <v>1428504</v>
+        <v>245.15</v>
       </c>
       <c r="D137" t="n">
-        <v>462049</v>
+        <v>245.15</v>
       </c>
       <c r="E137" t="n">
-        <v>32.34</v>
+        <v>918268</v>
+      </c>
+      <c r="F137" t="n">
+        <v>314634</v>
+      </c>
+      <c r="G137" t="n">
+        <v>34.26</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>219.84</v>
+        <v>246.55</v>
       </c>
       <c r="C138" t="n">
-        <v>634188</v>
+        <v>246.55</v>
       </c>
       <c r="D138" t="n">
-        <v>242494</v>
+        <v>246.55</v>
       </c>
       <c r="E138" t="n">
-        <v>38.24</v>
+        <v>668194</v>
+      </c>
+      <c r="F138" t="n">
+        <v>258680</v>
+      </c>
+      <c r="G138" t="n">
+        <v>38.71</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>219.06</v>
+        <v>246.55</v>
       </c>
       <c r="C139" t="n">
-        <v>2394418</v>
+        <v>246.55</v>
       </c>
       <c r="D139" t="n">
-        <v>585817</v>
+        <v>246.55</v>
       </c>
       <c r="E139" t="n">
-        <v>24.47</v>
+        <v>668194</v>
+      </c>
+      <c r="F139" t="n">
+        <v>258680</v>
+      </c>
+      <c r="G139" t="n">
+        <v>38.71</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>217.79</v>
+        <v>227.1</v>
       </c>
       <c r="C140" t="n">
-        <v>1600858</v>
+        <v>227.1</v>
       </c>
       <c r="D140" t="n">
-        <v>386891</v>
+        <v>227.1</v>
       </c>
       <c r="E140" t="n">
-        <v>24.17</v>
+        <v>1105874</v>
+      </c>
+      <c r="F140" t="n">
+        <v>467344</v>
+      </c>
+      <c r="G140" t="n">
+        <v>42.26</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>216.24</v>
+        <v>226.57</v>
       </c>
       <c r="C141" t="n">
-        <v>1837716</v>
+        <v>226.57</v>
       </c>
       <c r="D141" t="n">
-        <v>620819</v>
+        <v>226.57</v>
       </c>
       <c r="E141" t="n">
-        <v>33.78</v>
+        <v>1371586</v>
+      </c>
+      <c r="F141" t="n">
+        <v>750814</v>
+      </c>
+      <c r="G141" t="n">
+        <v>54.74</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>217.38</v>
+        <v>228.66</v>
       </c>
       <c r="C142" t="n">
-        <v>3715566</v>
+        <v>228.66</v>
       </c>
       <c r="D142" t="n">
-        <v>1276183</v>
+        <v>228.66</v>
       </c>
       <c r="E142" t="n">
-        <v>34.35</v>
+        <v>468319</v>
+      </c>
+      <c r="F142" t="n">
+        <v>267139</v>
+      </c>
+      <c r="G142" t="n">
+        <v>57.04</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>216.3</v>
+        <v>226.87</v>
       </c>
       <c r="C143" t="n">
-        <v>2736587</v>
+        <v>226.87</v>
       </c>
       <c r="D143" t="n">
-        <v>787274</v>
+        <v>226.87</v>
       </c>
       <c r="E143" t="n">
-        <v>28.77</v>
+        <v>516708</v>
+      </c>
+      <c r="F143" t="n">
+        <v>293088</v>
+      </c>
+      <c r="G143" t="n">
+        <v>56.72</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>220.09</v>
+        <v>216.24</v>
       </c>
       <c r="C144" t="n">
-        <v>1498077</v>
+        <v>216.24</v>
       </c>
       <c r="D144" t="n">
-        <v>716620</v>
+        <v>216.24</v>
       </c>
       <c r="E144" t="n">
-        <v>47.84</v>
+        <v>756389</v>
+      </c>
+      <c r="F144" t="n">
+        <v>433202</v>
+      </c>
+      <c r="G144" t="n">
+        <v>57.27</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>220.51</v>
+        <v>233.76</v>
       </c>
       <c r="C145" t="n">
-        <v>7806337</v>
+        <v>233.76</v>
       </c>
       <c r="D145" t="n">
-        <v>1501303</v>
+        <v>233.76</v>
       </c>
       <c r="E145" t="n">
-        <v>19.23</v>
+        <v>1694529</v>
+      </c>
+      <c r="F145" t="n">
+        <v>430919</v>
+      </c>
+      <c r="G145" t="n">
+        <v>25.43</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>217.94</v>
+        <v>227.14</v>
       </c>
       <c r="C146" t="n">
-        <v>6586147</v>
+        <v>227.14</v>
       </c>
       <c r="D146" t="n">
-        <v>1346218</v>
+        <v>227.14</v>
       </c>
       <c r="E146" t="n">
-        <v>20.44</v>
+        <v>1333469</v>
+      </c>
+      <c r="F146" t="n">
+        <v>656423</v>
+      </c>
+      <c r="G146" t="n">
+        <v>49.23</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>218.09</v>
+        <v>229.7</v>
       </c>
       <c r="C147" t="n">
-        <v>4084627</v>
+        <v>229.7</v>
       </c>
       <c r="D147" t="n">
-        <v>870200</v>
+        <v>229.7</v>
       </c>
       <c r="E147" t="n">
-        <v>21.3</v>
+        <v>558064</v>
+      </c>
+      <c r="F147" t="n">
+        <v>215891</v>
+      </c>
+      <c r="G147" t="n">
+        <v>38.69</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>213.43</v>
+        <v>235.7</v>
       </c>
       <c r="C148" t="n">
-        <v>2240521</v>
+        <v>235.7</v>
       </c>
       <c r="D148" t="n">
-        <v>1190939</v>
+        <v>235.7</v>
       </c>
       <c r="E148" t="n">
-        <v>53.15</v>
+        <v>1242149</v>
+      </c>
+      <c r="F148" t="n">
+        <v>590171</v>
+      </c>
+      <c r="G148" t="n">
+        <v>47.51</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>170.75</v>
+        <v>239.18</v>
       </c>
       <c r="C149" t="n">
-        <v>2912295</v>
+        <v>239.18</v>
       </c>
       <c r="D149" t="n">
-        <v>1271599</v>
+        <v>239.18</v>
       </c>
       <c r="E149" t="n">
-        <v>43.66</v>
+        <v>1285925</v>
+      </c>
+      <c r="F149" t="n">
+        <v>429171</v>
+      </c>
+      <c r="G149" t="n">
+        <v>33.37</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>136.6</v>
+        <v>241.9</v>
       </c>
       <c r="C150" t="n">
-        <v>171475</v>
+        <v>241.9</v>
       </c>
       <c r="D150" t="n">
-        <v>171475</v>
+        <v>241.9</v>
       </c>
       <c r="E150" t="n">
-        <v>100</v>
+        <v>1609258</v>
+      </c>
+      <c r="F150" t="n">
+        <v>780486</v>
+      </c>
+      <c r="G150" t="n">
+        <v>48.5</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>122.94</v>
+        <v>236.7</v>
       </c>
       <c r="C151" t="n">
-        <v>97492</v>
+        <v>236.7</v>
       </c>
       <c r="D151" t="n">
-        <v>97491</v>
+        <v>236.7</v>
       </c>
       <c r="E151" t="n">
-        <v>100</v>
+        <v>892642</v>
+      </c>
+      <c r="F151" t="n">
+        <v>351371</v>
+      </c>
+      <c r="G151" t="n">
+        <v>39.36</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>110.65</v>
+        <v>240.03</v>
       </c>
       <c r="C152" t="n">
-        <v>82995</v>
+        <v>240.03</v>
       </c>
       <c r="D152" t="n">
-        <v>82994</v>
+        <v>240.03</v>
       </c>
       <c r="E152" t="n">
-        <v>100</v>
+        <v>1275917</v>
+      </c>
+      <c r="F152" t="n">
+        <v>380688</v>
+      </c>
+      <c r="G152" t="n">
+        <v>29.84</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>99.59</v>
+        <v>238.09</v>
       </c>
       <c r="C153" t="n">
-        <v>204974</v>
+        <v>238.09</v>
       </c>
       <c r="D153" t="n">
-        <v>204974</v>
+        <v>238.09</v>
       </c>
       <c r="E153" t="n">
-        <v>100</v>
+        <v>1284474</v>
+      </c>
+      <c r="F153" t="n">
+        <v>604404</v>
+      </c>
+      <c r="G153" t="n">
+        <v>47.05</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B154" t="n">
+        <v>236.51</v>
+      </c>
+      <c r="C154" t="n">
+        <v>236.51</v>
+      </c>
+      <c r="D154" t="n">
+        <v>236.51</v>
+      </c>
+      <c r="E154" t="n">
+        <v>748214</v>
+      </c>
+      <c r="F154" t="n">
+        <v>243644</v>
+      </c>
+      <c r="G154" t="n">
+        <v>32.56</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B155" t="n">
+        <v>225.68</v>
+      </c>
+      <c r="C155" t="n">
+        <v>225.68</v>
+      </c>
+      <c r="D155" t="n">
+        <v>225.68</v>
+      </c>
+      <c r="E155" t="n">
+        <v>3789584</v>
+      </c>
+      <c r="F155" t="n">
+        <v>1194075</v>
+      </c>
+      <c r="G155" t="n">
+        <v>31.51</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B156" t="n">
+        <v>225.02</v>
+      </c>
+      <c r="C156" t="n">
+        <v>225.02</v>
+      </c>
+      <c r="D156" t="n">
+        <v>225.02</v>
+      </c>
+      <c r="E156" t="n">
+        <v>1980280</v>
+      </c>
+      <c r="F156" t="n">
+        <v>696136</v>
+      </c>
+      <c r="G156" t="n">
+        <v>35.15</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B157" t="n">
+        <v>231.57</v>
+      </c>
+      <c r="C157" t="n">
+        <v>231.57</v>
+      </c>
+      <c r="D157" t="n">
+        <v>231.57</v>
+      </c>
+      <c r="E157" t="n">
+        <v>1348473</v>
+      </c>
+      <c r="F157" t="n">
+        <v>836695</v>
+      </c>
+      <c r="G157" t="n">
+        <v>62.05</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B158" t="n">
+        <v>231.58</v>
+      </c>
+      <c r="C158" t="n">
+        <v>231.58</v>
+      </c>
+      <c r="D158" t="n">
+        <v>231.58</v>
+      </c>
+      <c r="E158" t="n">
+        <v>820685</v>
+      </c>
+      <c r="F158" t="n">
+        <v>394520</v>
+      </c>
+      <c r="G158" t="n">
+        <v>48.07</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B159" t="n">
+        <v>231.58</v>
+      </c>
+      <c r="C159" t="n">
+        <v>231.58</v>
+      </c>
+      <c r="D159" t="n">
+        <v>231.58</v>
+      </c>
+      <c r="E159" t="n">
+        <v>820685</v>
+      </c>
+      <c r="F159" t="n">
+        <v>394520</v>
+      </c>
+      <c r="G159" t="n">
+        <v>48.07</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B160" t="n">
+        <v>223.12</v>
+      </c>
+      <c r="C160" t="n">
+        <v>223.12</v>
+      </c>
+      <c r="D160" t="n">
+        <v>223.12</v>
+      </c>
+      <c r="E160" t="n">
+        <v>564135</v>
+      </c>
+      <c r="F160" t="n">
+        <v>254562</v>
+      </c>
+      <c r="G160" t="n">
+        <v>45.12</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B161" t="n">
+        <v>227.06</v>
+      </c>
+      <c r="C161" t="n">
+        <v>227.06</v>
+      </c>
+      <c r="D161" t="n">
+        <v>227.06</v>
+      </c>
+      <c r="E161" t="n">
+        <v>592516</v>
+      </c>
+      <c r="F161" t="n">
+        <v>258309</v>
+      </c>
+      <c r="G161" t="n">
+        <v>43.6</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B162" t="n">
+        <v>234.31</v>
+      </c>
+      <c r="C162" t="n">
+        <v>234.31</v>
+      </c>
+      <c r="D162" t="n">
+        <v>234.31</v>
+      </c>
+      <c r="E162" t="n">
+        <v>1140218</v>
+      </c>
+      <c r="F162" t="n">
+        <v>421273</v>
+      </c>
+      <c r="G162" t="n">
+        <v>36.95</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B163" t="n">
+        <v>248.43</v>
+      </c>
+      <c r="C163" t="n">
+        <v>248.43</v>
+      </c>
+      <c r="D163" t="n">
+        <v>248.43</v>
+      </c>
+      <c r="E163" t="n">
+        <v>2447922</v>
+      </c>
+      <c r="F163" t="n">
+        <v>627209</v>
+      </c>
+      <c r="G163" t="n">
+        <v>25.62</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B164" t="n">
+        <v>253.38</v>
+      </c>
+      <c r="C164" t="n">
+        <v>253.38</v>
+      </c>
+      <c r="D164" t="n">
+        <v>253.38</v>
+      </c>
+      <c r="E164" t="n">
+        <v>1778621</v>
+      </c>
+      <c r="F164" t="n">
+        <v>489187</v>
+      </c>
+      <c r="G164" t="n">
+        <v>27.5</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B165" t="n">
+        <v>240.72</v>
+      </c>
+      <c r="C165" t="n">
+        <v>240.72</v>
+      </c>
+      <c r="D165" t="n">
+        <v>240.72</v>
+      </c>
+      <c r="E165" t="n">
+        <v>1803394</v>
+      </c>
+      <c r="F165" t="n">
+        <v>342209</v>
+      </c>
+      <c r="G165" t="n">
+        <v>18.98</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B166" t="n">
+        <v>224.89</v>
+      </c>
+      <c r="C166" t="n">
+        <v>224.89</v>
+      </c>
+      <c r="D166" t="n">
+        <v>224.89</v>
+      </c>
+      <c r="E166" t="n">
+        <v>820448</v>
+      </c>
+      <c r="F166" t="n">
+        <v>347187</v>
+      </c>
+      <c r="G166" t="n">
+        <v>42.32</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B167" t="n">
+        <v>216.1</v>
+      </c>
+      <c r="C167" t="n">
+        <v>216.1</v>
+      </c>
+      <c r="D167" t="n">
+        <v>216.1</v>
+      </c>
+      <c r="E167" t="n">
+        <v>982645</v>
+      </c>
+      <c r="F167" t="n">
+        <v>396992</v>
+      </c>
+      <c r="G167" t="n">
+        <v>40.4</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B168" t="n">
+        <v>216.6</v>
+      </c>
+      <c r="C168" t="n">
+        <v>216.6</v>
+      </c>
+      <c r="D168" t="n">
+        <v>216.6</v>
+      </c>
+      <c r="E168" t="n">
+        <v>491358</v>
+      </c>
+      <c r="F168" t="n">
+        <v>289592</v>
+      </c>
+      <c r="G168" t="n">
+        <v>58.94</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B169" t="n">
+        <v>218.41</v>
+      </c>
+      <c r="C169" t="n">
+        <v>218.41</v>
+      </c>
+      <c r="D169" t="n">
+        <v>218.41</v>
+      </c>
+      <c r="E169" t="n">
+        <v>776940</v>
+      </c>
+      <c r="F169" t="n">
+        <v>462061</v>
+      </c>
+      <c r="G169" t="n">
+        <v>59.47</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B170" t="n">
+        <v>216.93</v>
+      </c>
+      <c r="C170" t="n">
+        <v>216.93</v>
+      </c>
+      <c r="D170" t="n">
+        <v>216.93</v>
+      </c>
+      <c r="E170" t="n">
+        <v>589194</v>
+      </c>
+      <c r="F170" t="n">
+        <v>252248</v>
+      </c>
+      <c r="G170" t="n">
+        <v>42.81</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B171" t="n">
+        <v>216.15</v>
+      </c>
+      <c r="C171" t="n">
+        <v>216.15</v>
+      </c>
+      <c r="D171" t="n">
+        <v>216.15</v>
+      </c>
+      <c r="E171" t="n">
+        <v>737195</v>
+      </c>
+      <c r="F171" t="n">
+        <v>401496</v>
+      </c>
+      <c r="G171" t="n">
+        <v>54.46</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B172" t="n">
+        <v>215.48</v>
+      </c>
+      <c r="C172" t="n">
+        <v>215.48</v>
+      </c>
+      <c r="D172" t="n">
+        <v>215.48</v>
+      </c>
+      <c r="E172" t="n">
+        <v>2051164</v>
+      </c>
+      <c r="F172" t="n">
+        <v>709077</v>
+      </c>
+      <c r="G172" t="n">
+        <v>34.57</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B173" t="n">
+        <v>219.17</v>
+      </c>
+      <c r="C173" t="n">
+        <v>219.17</v>
+      </c>
+      <c r="D173" t="n">
+        <v>219.17</v>
+      </c>
+      <c r="E173" t="n">
+        <v>1428504</v>
+      </c>
+      <c r="F173" t="n">
+        <v>462049</v>
+      </c>
+      <c r="G173" t="n">
+        <v>32.34</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B174" t="n">
+        <v>219.84</v>
+      </c>
+      <c r="C174" t="n">
+        <v>219.84</v>
+      </c>
+      <c r="D174" t="n">
+        <v>219.84</v>
+      </c>
+      <c r="E174" t="n">
+        <v>634188</v>
+      </c>
+      <c r="F174" t="n">
+        <v>242494</v>
+      </c>
+      <c r="G174" t="n">
+        <v>38.24</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B175" t="n">
+        <v>219.06</v>
+      </c>
+      <c r="C175" t="n">
+        <v>219.06</v>
+      </c>
+      <c r="D175" t="n">
+        <v>219.06</v>
+      </c>
+      <c r="E175" t="n">
+        <v>2394418</v>
+      </c>
+      <c r="F175" t="n">
+        <v>585817</v>
+      </c>
+      <c r="G175" t="n">
+        <v>24.47</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B176" t="n">
+        <v>217.79</v>
+      </c>
+      <c r="C176" t="n">
+        <v>217.79</v>
+      </c>
+      <c r="D176" t="n">
+        <v>217.79</v>
+      </c>
+      <c r="E176" t="n">
+        <v>1600858</v>
+      </c>
+      <c r="F176" t="n">
+        <v>386891</v>
+      </c>
+      <c r="G176" t="n">
+        <v>24.17</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B177" t="n">
+        <v>216.24</v>
+      </c>
+      <c r="C177" t="n">
+        <v>216.24</v>
+      </c>
+      <c r="D177" t="n">
+        <v>216.24</v>
+      </c>
+      <c r="E177" t="n">
+        <v>1837716</v>
+      </c>
+      <c r="F177" t="n">
+        <v>620819</v>
+      </c>
+      <c r="G177" t="n">
+        <v>33.78</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B178" t="n">
+        <v>217.38</v>
+      </c>
+      <c r="C178" t="n">
+        <v>217.38</v>
+      </c>
+      <c r="D178" t="n">
+        <v>217.38</v>
+      </c>
+      <c r="E178" t="n">
+        <v>3715566</v>
+      </c>
+      <c r="F178" t="n">
+        <v>1276183</v>
+      </c>
+      <c r="G178" t="n">
+        <v>34.35</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B179" t="n">
+        <v>216.3</v>
+      </c>
+      <c r="C179" t="n">
+        <v>216.3</v>
+      </c>
+      <c r="D179" t="n">
+        <v>216.3</v>
+      </c>
+      <c r="E179" t="n">
+        <v>2736587</v>
+      </c>
+      <c r="F179" t="n">
+        <v>787274</v>
+      </c>
+      <c r="G179" t="n">
+        <v>28.77</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B180" t="n">
+        <v>220.09</v>
+      </c>
+      <c r="C180" t="n">
+        <v>220.09</v>
+      </c>
+      <c r="D180" t="n">
+        <v>220.09</v>
+      </c>
+      <c r="E180" t="n">
+        <v>1498077</v>
+      </c>
+      <c r="F180" t="n">
+        <v>716620</v>
+      </c>
+      <c r="G180" t="n">
+        <v>47.84</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B181" t="n">
+        <v>220.51</v>
+      </c>
+      <c r="C181" t="n">
+        <v>220.51</v>
+      </c>
+      <c r="D181" t="n">
+        <v>220.51</v>
+      </c>
+      <c r="E181" t="n">
+        <v>7806337</v>
+      </c>
+      <c r="F181" t="n">
+        <v>1501303</v>
+      </c>
+      <c r="G181" t="n">
+        <v>19.23</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B182" t="n">
+        <v>217.94</v>
+      </c>
+      <c r="C182" t="n">
+        <v>217.94</v>
+      </c>
+      <c r="D182" t="n">
+        <v>217.94</v>
+      </c>
+      <c r="E182" t="n">
+        <v>6586147</v>
+      </c>
+      <c r="F182" t="n">
+        <v>1346218</v>
+      </c>
+      <c r="G182" t="n">
+        <v>20.44</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B183" t="n">
+        <v>218.09</v>
+      </c>
+      <c r="C183" t="n">
+        <v>218.09</v>
+      </c>
+      <c r="D183" t="n">
+        <v>218.09</v>
+      </c>
+      <c r="E183" t="n">
+        <v>4084627</v>
+      </c>
+      <c r="F183" t="n">
+        <v>870200</v>
+      </c>
+      <c r="G183" t="n">
+        <v>21.3</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B184" t="n">
+        <v>213.43</v>
+      </c>
+      <c r="C184" t="n">
+        <v>213.43</v>
+      </c>
+      <c r="D184" t="n">
+        <v>213.43</v>
+      </c>
+      <c r="E184" t="n">
+        <v>2240521</v>
+      </c>
+      <c r="F184" t="n">
+        <v>1190939</v>
+      </c>
+      <c r="G184" t="n">
+        <v>53.15</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B185" t="n">
+        <v>170.75</v>
+      </c>
+      <c r="C185" t="n">
+        <v>170.75</v>
+      </c>
+      <c r="D185" t="n">
+        <v>170.75</v>
+      </c>
+      <c r="E185" t="n">
+        <v>2912295</v>
+      </c>
+      <c r="F185" t="n">
+        <v>1271599</v>
+      </c>
+      <c r="G185" t="n">
+        <v>43.66</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B186" t="n">
+        <v>136.6</v>
+      </c>
+      <c r="C186" t="n">
+        <v>136.6</v>
+      </c>
+      <c r="D186" t="n">
+        <v>136.6</v>
+      </c>
+      <c r="E186" t="n">
+        <v>171475</v>
+      </c>
+      <c r="F186" t="n">
+        <v>171475</v>
+      </c>
+      <c r="G186" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B187" t="n">
+        <v>122.94</v>
+      </c>
+      <c r="C187" t="n">
+        <v>122.94</v>
+      </c>
+      <c r="D187" t="n">
+        <v>122.94</v>
+      </c>
+      <c r="E187" t="n">
+        <v>97492</v>
+      </c>
+      <c r="F187" t="n">
+        <v>97491</v>
+      </c>
+      <c r="G187" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B188" t="n">
+        <v>110.65</v>
+      </c>
+      <c r="C188" t="n">
+        <v>110.65</v>
+      </c>
+      <c r="D188" t="n">
+        <v>110.65</v>
+      </c>
+      <c r="E188" t="n">
+        <v>82995</v>
+      </c>
+      <c r="F188" t="n">
+        <v>82994</v>
+      </c>
+      <c r="G188" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B189" t="n">
+        <v>99.59</v>
+      </c>
+      <c r="C189" t="n">
+        <v>99.59</v>
+      </c>
+      <c r="D189" t="n">
+        <v>99.59</v>
+      </c>
+      <c r="E189" t="n">
+        <v>204974</v>
+      </c>
+      <c r="F189" t="n">
+        <v>204974</v>
+      </c>
+      <c r="G189" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="B154" t="n">
+      <c r="B190" t="n">
         <v>94.62</v>
       </c>
-      <c r="C154" t="n">
+      <c r="C190" t="n">
+        <v>94.62</v>
+      </c>
+      <c r="D190" t="n">
+        <v>94.62</v>
+      </c>
+      <c r="E190" t="n">
         <v>381164</v>
       </c>
-      <c r="D154" t="n">
+      <c r="F190" t="n">
         <v>381164</v>
       </c>
-      <c r="E154" t="n">
+      <c r="G190" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B191" t="n">
+        <v>89.89</v>
+      </c>
+      <c r="C191" t="n">
+        <v>89.89</v>
+      </c>
+      <c r="D191" t="n">
+        <v>89.89</v>
+      </c>
+      <c r="E191" t="n">
+        <v>164141</v>
+      </c>
+      <c r="F191" t="n">
+        <v>164141</v>
+      </c>
+      <c r="G191" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B192" t="n">
+        <v>85.40000000000001</v>
+      </c>
+      <c r="C192" t="n">
+        <v>85.40000000000001</v>
+      </c>
+      <c r="D192" t="n">
+        <v>85.40000000000001</v>
+      </c>
+      <c r="E192" t="n">
+        <v>71897</v>
+      </c>
+      <c r="F192" t="n">
+        <v>71897</v>
+      </c>
+      <c r="G192" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B193" t="n">
+        <v>81.13</v>
+      </c>
+      <c r="C193" t="n">
+        <v>81.13</v>
+      </c>
+      <c r="D193" t="n">
+        <v>81.13</v>
+      </c>
+      <c r="E193" t="n">
+        <v>38995</v>
+      </c>
+      <c r="F193" t="n">
+        <v>38995</v>
+      </c>
+      <c r="G193" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B194" t="n">
+        <v>77.08</v>
+      </c>
+      <c r="C194" t="n">
+        <v>77.08</v>
+      </c>
+      <c r="D194" t="n">
+        <v>77.08</v>
+      </c>
+      <c r="E194" t="n">
+        <v>54315</v>
+      </c>
+      <c r="F194" t="n">
+        <v>54315</v>
+      </c>
+      <c r="G194" t="n">
         <v>100</v>
       </c>
     </row>
